--- a/data/trans_orig/Q02D_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q02D_R-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas diarias, a la semana, que dedica la persona entrevistada a cuidar a las personas del hogar que lo necesitan</t>
+          <t>Número medio de horas diarias, a la semana, que dedica la persona entrevistada a cuidar a las personas del hogar que lo necesitan (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 3,92</t>
+          <t>2,62; 4,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,26; 5,33</t>
+          <t>4,26; 5,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 7,37</t>
+          <t>5,67; 7,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 8,94</t>
+          <t>5,39; 8,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 5,75</t>
+          <t>4,39; 5,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,29; 7,26</t>
+          <t>6,33; 7,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,36; 9,01</t>
+          <t>7,37; 9,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,44; 10,61</t>
+          <t>7,48; 10,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,86; 4,86</t>
+          <t>3,85; 4,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,57; 6,35</t>
+          <t>5,59; 6,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,81; 8,02</t>
+          <t>6,79; 8,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,87; 9,33</t>
+          <t>6,98; 9,21</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,55; 5,02</t>
+          <t>3,56; 5,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 5,62</t>
+          <t>4,77; 5,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 6,36</t>
+          <t>5,04; 6,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,69; 7,15</t>
+          <t>4,75; 7,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,63; 6,92</t>
+          <t>5,59; 6,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,36; 7,24</t>
+          <t>6,34; 7,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 8,53</t>
+          <t>7,35; 8,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,76; 8,41</t>
+          <t>6,79; 8,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 5,94</t>
+          <t>4,87; 5,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 6,4</t>
+          <t>5,85; 6,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 7,46</t>
+          <t>6,54; 7,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,31; 7,67</t>
+          <t>6,27; 7,58</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,35</t>
+          <t>3,9; 5,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,46; 5,38</t>
+          <t>4,51; 5,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,79; 9,71</t>
+          <t>7,75; 9,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,46; 12,37</t>
+          <t>4,5; 12,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 7,59</t>
+          <t>6,0; 7,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 7,35</t>
+          <t>6,51; 7,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,3; 12,17</t>
+          <t>10,3; 12,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,51; 10,98</t>
+          <t>7,57; 10,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,31; 6,49</t>
+          <t>5,31; 6,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,85; 6,51</t>
+          <t>5,84; 6,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,58; 10,89</t>
+          <t>9,58; 10,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,16; 10,39</t>
+          <t>6,98; 10,18</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 4,74</t>
+          <t>3,43; 4,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,3; 5,22</t>
+          <t>4,31; 5,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,78; 8,44</t>
+          <t>6,7; 8,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,86; 8,23</t>
+          <t>4,77; 8,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,14; 7,53</t>
+          <t>6,15; 7,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 7,01</t>
+          <t>6,22; 6,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,32; 9,79</t>
+          <t>8,33; 9,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,06; 8,55</t>
+          <t>6,13; 8,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,29; 6,32</t>
+          <t>5,18; 6,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,59; 6,18</t>
+          <t>5,55; 6,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,92; 9,09</t>
+          <t>7,91; 9,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,86</t>
+          <t>5,84; 7,91</t>
         </is>
       </c>
     </row>
@@ -1276,42 +1276,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 4,33</t>
+          <t>3,65; 4,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,7; 5,16</t>
+          <t>4,68; 5,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,5; 7,33</t>
+          <t>6,5; 7,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,5; 7,34</t>
+          <t>5,48; 7,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,86; 6,55</t>
+          <t>5,87; 6,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,55; 6,97</t>
+          <t>6,55; 6,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,56; 9,36</t>
+          <t>8,59; 9,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,4; 8,58</t>
+          <t>7,41; 8,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,83; 8,4</t>
+          <t>7,84; 8,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,94</t>
+          <t>6,82; 7,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q02D_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q02D_R-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,84</t>
+          <t>6,57</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,72</t>
+          <t>8,54</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,93</t>
+          <t>7,71</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,05</t>
+          <t>2,64; 3,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,26; 5,38</t>
+          <t>4,23; 5,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,67; 7,41</t>
+          <t>5,65; 7,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 8,74</t>
+          <t>5,19; 8,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 5,71</t>
+          <t>4,37; 5,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -746,32 +746,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,03</t>
+          <t>7,38; 9,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,48; 10,89</t>
+          <t>7,31; 10,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,85; 4,83</t>
+          <t>3,85; 4,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,59; 6,34</t>
+          <t>5,57; 6,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,79; 8,04</t>
+          <t>6,78; 8,06</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,98; 9,21</t>
+          <t>6,69; 9,1</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,76</t>
+          <t>6,04</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,56</t>
+          <t>7,48</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,9</t>
+          <t>6,91</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 5,07</t>
+          <t>3,58; 5,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 5,61</t>
+          <t>4,77; 5,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 6,29</t>
+          <t>5,1; 6,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,75; 7,19</t>
+          <t>4,96; 7,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,59; 6,94</t>
+          <t>5,64; 7,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,34; 7,17</t>
+          <t>6,38; 7,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,35; 8,56</t>
+          <t>7,31; 8,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,79; 8,41</t>
+          <t>6,74; 8,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 5,91</t>
+          <t>4,93; 5,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 6,47</t>
+          <t>5,81; 6,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,54; 7,46</t>
+          <t>6,56; 7,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,27; 7,58</t>
+          <t>6,31; 7,66</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,01</t>
+          <t>6,68</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,95</t>
+          <t>8,91</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,37</t>
+          <t>8,24</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 5,38</t>
+          <t>3,88; 5,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 5,38</t>
+          <t>4,47; 5,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,75; 9,74</t>
+          <t>7,71; 9,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,5; 12,17</t>
+          <t>4,53; 11,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 7,56</t>
+          <t>6,0; 7,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 7,39</t>
+          <t>6,5; 7,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,3; 12,1</t>
+          <t>10,33; 12,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,57; 10,78</t>
+          <t>7,61; 10,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,31; 6,54</t>
+          <t>5,33; 6,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,84; 6,52</t>
+          <t>5,86; 6,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,58; 10,91</t>
+          <t>9,63; 10,92</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,98; 10,18</t>
+          <t>6,98; 9,81</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,93</t>
+          <t>5,56</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,13</t>
+          <t>7,38</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,66</t>
+          <t>6,67</t>
         </is>
       </c>
     </row>
@@ -1136,47 +1136,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 4,62</t>
+          <t>3,39; 4,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 5,21</t>
+          <t>4,28; 5,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 8,32</t>
+          <t>6,65; 8,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,77; 8,11</t>
+          <t>4,63; 7,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,15; 7,58</t>
+          <t>6,15; 7,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 6,98</t>
+          <t>6,22; 7,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,33; 9,77</t>
+          <t>8,32; 9,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,13; 8,71</t>
+          <t>6,28; 8,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 6,27</t>
+          <t>5,24; 6,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,91; 9,01</t>
+          <t>7,85; 8,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 7,91</t>
+          <t>5,89; 7,68</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,23</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,96</t>
+          <t>7,93</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>7,24</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 4,34</t>
+          <t>3,65; 4,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,68; 5,13</t>
+          <t>4,69; 5,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1291,47 +1291,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,48; 7,29</t>
+          <t>5,45; 7,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 6,55</t>
+          <t>5,85; 6,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,55; 6,98</t>
+          <t>6,57; 6,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,59; 9,37</t>
+          <t>8,58; 9,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 8,69</t>
+          <t>7,42; 8,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,11; 5,64</t>
+          <t>5,08; 5,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 6,19</t>
+          <t>5,88; 6,2</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,84; 8,44</t>
+          <t>7,86; 8,45</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,84</t>
+          <t>6,78; 7,74</t>
         </is>
       </c>
     </row>
